--- a/Rhubarb_7_1_C.xlsx
+++ b/Rhubarb_7_1_C.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="493">
   <si>
     <t>UP</t>
   </si>
@@ -1325,12 +1325,6 @@
     <t>Pleat Count</t>
   </si>
   <si>
-    <t>RhubarbTemplate</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
     <t>2016-05-12</t>
   </si>
   <si>
@@ -1367,9 +1361,6 @@
     <t>person@company.com</t>
   </si>
   <si>
-    <t>FGHJ</t>
-  </si>
-  <si>
     <t>ComponentPartNumber</t>
   </si>
   <si>
@@ -1527,6 +1518,9 @@
   </si>
   <si>
     <t>123456789012345678901234567</t>
+  </si>
+  <si>
+    <t>WXYZ</t>
   </si>
 </sst>
 </file>
@@ -1720,8 +1714,8 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF00"/>
       <color rgb="FFFFFF66"/>
-      <color rgb="FFFFFF00"/>
       <color rgb="FFFFFF99"/>
       <color rgb="FFFFFFCC"/>
     </mruColors>
@@ -2000,7 +1994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -2011,21 +2005,21 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>427</v>
+        <v>57</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>428</v>
+        <v>476</v>
       </c>
       <c r="F1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>479</v>
+        <v>58</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>438</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" t="str">
@@ -2034,11 +2028,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>440</v>
+      <c r="A3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="F3" s="8"/>
       <c r="G3" t="str">
@@ -2047,11 +2041,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>84</v>
+      <c r="A4" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" t="str">
@@ -2061,10 +2055,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F5" s="22"/>
       <c r="G5" t="str">
@@ -2074,105 +2068,97 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>82</v>
+      <c r="A8" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>87</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>441</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>65</v>
+      <c r="A13" s="23" t="s">
+        <v>83</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>88</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>83</v>
+      <c r="A14" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>480</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="10" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2181,7 +2167,7 @@
     <sortCondition sortBy="cellColor" ref="A2:A15" dxfId="0"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2504,7 +2490,7 @@
         <v>32</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q2" t="s">
         <v>163</v>
@@ -2554,7 +2540,7 @@
         <v>32</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q3" t="s">
         <v>163</v>
@@ -2604,7 +2590,7 @@
         <v>32</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q4" t="s">
         <v>163</v>
@@ -2654,7 +2640,7 @@
         <v>32</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q5" t="s">
         <v>163</v>
@@ -2704,7 +2690,7 @@
         <v>32</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q6" t="s">
         <v>163</v>
@@ -2754,7 +2740,7 @@
         <v>32</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q7" t="s">
         <v>163</v>
@@ -2804,7 +2790,7 @@
         <v>32</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q8" t="s">
         <v>163</v>
@@ -2854,7 +2840,7 @@
         <v>32</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q9" t="s">
         <v>163</v>
@@ -2904,7 +2890,7 @@
         <v>32</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q10" t="s">
         <v>163</v>
@@ -2954,7 +2940,7 @@
         <v>32</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q11" t="s">
         <v>163</v>
@@ -3004,7 +2990,7 @@
         <v>32</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q12" t="s">
         <v>163</v>
@@ -3054,7 +3040,7 @@
         <v>32</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q13" t="s">
         <v>163</v>
@@ -3104,7 +3090,7 @@
         <v>32</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q14" t="s">
         <v>163</v>
@@ -3154,7 +3140,7 @@
         <v>32</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q15" t="s">
         <v>163</v>
@@ -3204,7 +3190,7 @@
         <v>32</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q16" t="s">
         <v>163</v>
@@ -3254,7 +3240,7 @@
         <v>32</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q17" t="s">
         <v>163</v>
@@ -3304,7 +3290,7 @@
         <v>32</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q18" t="s">
         <v>163</v>
@@ -3354,7 +3340,7 @@
         <v>32</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q19" t="s">
         <v>163</v>
@@ -3404,7 +3390,7 @@
         <v>32</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q20" t="s">
         <v>163</v>
@@ -3454,7 +3440,7 @@
         <v>32</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q21" t="s">
         <v>163</v>
@@ -3504,7 +3490,7 @@
         <v>32</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q22" t="s">
         <v>163</v>
@@ -3554,7 +3540,7 @@
         <v>32</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q23" t="s">
         <v>163</v>
@@ -3604,7 +3590,7 @@
         <v>32</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q24" t="s">
         <v>163</v>
@@ -3654,7 +3640,7 @@
         <v>32</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q25" t="s">
         <v>163</v>
@@ -3704,7 +3690,7 @@
         <v>32</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q26" t="s">
         <v>163</v>
@@ -3754,7 +3740,7 @@
         <v>32</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q27" t="s">
         <v>163</v>
@@ -3804,7 +3790,7 @@
         <v>32</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q28" t="s">
         <v>163</v>
@@ -3854,7 +3840,7 @@
         <v>32</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q29" t="s">
         <v>163</v>
@@ -3904,7 +3890,7 @@
         <v>32</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q30" t="s">
         <v>163</v>
@@ -3954,7 +3940,7 @@
         <v>32</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q31" t="s">
         <v>163</v>
@@ -4004,7 +3990,7 @@
         <v>32</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="Q32" t="s">
         <v>163</v>
@@ -4054,7 +4040,7 @@
         <v>32</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q33" t="s">
         <v>163</v>
@@ -4104,7 +4090,7 @@
         <v>32</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q34" t="s">
         <v>163</v>
@@ -4154,7 +4140,7 @@
         <v>32</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q35" t="s">
         <v>163</v>
@@ -4204,7 +4190,7 @@
         <v>32</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q36" t="s">
         <v>163</v>
@@ -4254,7 +4240,7 @@
         <v>32</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q37" t="s">
         <v>163</v>
@@ -4304,7 +4290,7 @@
         <v>32</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q38" t="s">
         <v>163</v>
@@ -4354,7 +4340,7 @@
         <v>32</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q39" t="s">
         <v>163</v>
@@ -4404,7 +4390,7 @@
         <v>32</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q40" t="s">
         <v>163</v>
@@ -4454,7 +4440,7 @@
         <v>32</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q41" t="s">
         <v>163</v>
@@ -4504,7 +4490,7 @@
         <v>32</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q42" t="s">
         <v>163</v>
@@ -4554,7 +4540,7 @@
         <v>32</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q43" t="s">
         <v>163</v>
@@ -4604,7 +4590,7 @@
         <v>32</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q44" t="s">
         <v>163</v>
@@ -4654,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q45" t="s">
         <v>163</v>
@@ -4704,7 +4690,7 @@
         <v>32</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q46" t="s">
         <v>163</v>
@@ -4754,7 +4740,7 @@
         <v>32</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q47" t="s">
         <v>163</v>
@@ -4804,7 +4790,7 @@
         <v>32</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="Q48" t="s">
         <v>163</v>
@@ -4854,7 +4840,7 @@
         <v>32</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q49" t="s">
         <v>163</v>
@@ -4904,7 +4890,7 @@
         <v>32</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q50" t="s">
         <v>163</v>
@@ -4954,7 +4940,7 @@
         <v>32</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q51" t="s">
         <v>163</v>
@@ -5004,7 +4990,7 @@
         <v>32</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q52" t="s">
         <v>163</v>
@@ -5054,7 +5040,7 @@
         <v>32</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q53" t="s">
         <v>163</v>
@@ -5104,7 +5090,7 @@
         <v>32</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Q54" t="s">
         <v>163</v>
@@ -5154,7 +5140,7 @@
         <v>32</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="Q55" t="s">
         <v>163</v>
@@ -5204,7 +5190,7 @@
         <v>32</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q56" t="s">
         <v>163</v>
@@ -5254,7 +5240,7 @@
         <v>32</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q57" t="s">
         <v>163</v>
@@ -5304,7 +5290,7 @@
         <v>32</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q58" t="s">
         <v>163</v>
@@ -5354,7 +5340,7 @@
         <v>32</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q59" t="s">
         <v>163</v>
@@ -5404,7 +5390,7 @@
         <v>32</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q60" t="s">
         <v>163</v>
@@ -5454,7 +5440,7 @@
         <v>32</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q61" t="s">
         <v>163</v>
@@ -5504,7 +5490,7 @@
         <v>32</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q62" t="s">
         <v>163</v>
@@ -5554,7 +5540,7 @@
         <v>32</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="Q63" t="s">
         <v>163</v>
@@ -5604,7 +5590,7 @@
         <v>32</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="Q64" t="s">
         <v>163</v>
@@ -5654,7 +5640,7 @@
         <v>32</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q65" t="s">
         <v>163</v>
@@ -5704,7 +5690,7 @@
         <v>32</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q66" t="s">
         <v>163</v>
@@ -5754,7 +5740,7 @@
         <v>32</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="Q67" t="s">
         <v>163</v>
@@ -5804,7 +5790,7 @@
         <v>32</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q68" t="s">
         <v>163</v>
@@ -5854,7 +5840,7 @@
         <v>32</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q69" t="s">
         <v>163</v>
@@ -5961,16 +5947,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="8" t="s">
         <v>68</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -6191,13 +6177,13 @@
         <v>45</v>
       </c>
       <c r="V1" s="18" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="W1" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="X1" s="18" t="s">
         <v>485</v>
-      </c>
-      <c r="X1" s="18" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
@@ -6211,7 +6197,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>0</v>
@@ -6260,7 +6246,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>0</v>
@@ -6309,7 +6295,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>0</v>
@@ -6357,19 +6343,19 @@
         <v>425</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
@@ -6383,7 +6369,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>0</v>
@@ -6423,7 +6409,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B6" s="3">
         <v>6832</v>
@@ -6432,7 +6418,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>0</v>
@@ -6481,7 +6467,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>0</v>
@@ -6530,7 +6516,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>0</v>
@@ -6625,10 +6611,10 @@
         <v>182</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>52</v>
@@ -6724,10 +6710,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>53</v>
@@ -6741,10 +6727,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>53</v>
@@ -6991,7 +6977,7 @@
         <v>179</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I5" t="s">
         <v>192</v>
@@ -7088,7 +7074,7 @@
         <v>266</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>52</v>
@@ -7682,10 +7668,10 @@
         <v>132</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J6">
         <v>10.5</v>
@@ -7709,7 +7695,7 @@
         <v>123</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="R6">
         <v>8</v>
@@ -7736,43 +7722,43 @@
         <v>49</v>
       </c>
       <c r="Z6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AA6" t="s">
         <v>29</v>
       </c>
       <c r="AB6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AC6" t="s">
         <v>78</v>
       </c>
       <c r="AD6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AE6">
         <v>123456</v>
       </c>
       <c r="AF6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AG6" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AH6" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AI6" t="s">
         <v>163</v>
       </c>
       <c r="AJ6" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AK6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AL6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AM6" t="s">
         <v>52</v>
@@ -7851,45 +7837,45 @@
         <v>47</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>448</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>451</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>48</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>450</v>
-      </c>
       <c r="J1" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="M1" s="22" t="s">
         <v>442</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="N1" s="22" t="s">
         <v>443</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>444</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>445</v>
-      </c>
-      <c r="N1" s="22" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C2" t="s">
         <v>53</v>
@@ -7913,27 +7899,27 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="K2" t="s">
         <v>78</v>
       </c>
       <c r="L2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="M2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="N2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C3" t="s">
         <v>53</v>
@@ -7953,10 +7939,10 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C4" t="s">
         <v>53</v>
